--- a/Test Data/Regression/4689052/UK_InHeader_ImportTb02.xlsx
+++ b/Test Data/Regression/4689052/UK_InHeader_ImportTb02.xlsx
@@ -23,13 +23,13 @@
     <t>test Description</t>
   </si>
   <si>
-    <t>2222243_PWE01_1777710138897</t>
-  </si>
-  <si>
-    <t>2222243_PWE02_1777710138897</t>
-  </si>
-  <si>
-    <t>2222243_PWE03_1777710138897</t>
+    <t>2222243_PWE01_1777802282650</t>
+  </si>
+  <si>
+    <t>2222243_PWE02_1777802282650</t>
+  </si>
+  <si>
+    <t>2222243_PWE03_1777802282650</t>
   </si>
   <si>
     <t>Sale of goods, UK</t>

--- a/Test Data/Regression/4689052/UK_InHeader_ImportTb02.xlsx
+++ b/Test Data/Regression/4689052/UK_InHeader_ImportTb02.xlsx
@@ -23,13 +23,13 @@
     <t>test Description</t>
   </si>
   <si>
-    <t>2222243_PWE01_1777802282650</t>
-  </si>
-  <si>
-    <t>2222243_PWE02_1777802282650</t>
-  </si>
-  <si>
-    <t>2222243_PWE03_1777802282650</t>
+    <t>2222243_PWE01_1777804357663</t>
+  </si>
+  <si>
+    <t>2222243_PWE02_1777804357663</t>
+  </si>
+  <si>
+    <t>2222243_PWE03_1777804357663</t>
   </si>
   <si>
     <t>Sale of goods, UK</t>

--- a/Test Data/Regression/4689052/UK_InHeader_ImportTb02.xlsx
+++ b/Test Data/Regression/4689052/UK_InHeader_ImportTb02.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>test Code</t>
   </si>
@@ -23,13 +23,13 @@
     <t>test Description</t>
   </si>
   <si>
-    <t>2222243_PWE01_1777804357663</t>
-  </si>
-  <si>
-    <t>2222243_PWE02_1777804357663</t>
-  </si>
-  <si>
-    <t>2222243_PWE03_1777804357663</t>
+    <t>2222244_PWE01_1777825842053</t>
+  </si>
+  <si>
+    <t>2222244_PWE02_1777825842053</t>
+  </si>
+  <si>
+    <t>2222244_PWE03_1777825842053</t>
   </si>
   <si>
     <t>Sale of goods, UK</t>
@@ -65,9 +65,6 @@
     <t>Redundancy costs</t>
   </si>
   <si>
-    <t>Rent and rates</t>
-  </si>
-  <si>
     <t>Rent</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
   </si>
   <si>
     <t>Computer software and maintenance costs</t>
-  </si>
-  <si>
-    <t>Printing, postage and stationery</t>
   </si>
   <si>
     <t>Staff training</t>
@@ -510,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="56.1796875" customWidth="1"/>
@@ -776,494 +770,460 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
       <c r="C16">
-        <v>83372.91</v>
+        <v>189604.9</v>
       </c>
       <c r="D16">
-        <v>83372.91</v>
+        <v>189604.9</v>
       </c>
       <c r="E16">
-        <v>83372.91</v>
+        <v>189604.9</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
       </c>
       <c r="C17">
-        <v>189604.9</v>
+        <v>31836</v>
       </c>
       <c r="D17">
-        <v>189604.9</v>
+        <v>31836</v>
       </c>
       <c r="E17">
-        <v>189604.9</v>
+        <v>31836</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
       </c>
       <c r="C18">
-        <v>31836</v>
+        <v>294511.42</v>
       </c>
       <c r="D18">
-        <v>31836</v>
+        <v>294511.42</v>
       </c>
       <c r="E18">
-        <v>31836</v>
+        <v>294511.42</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B19" t="s">
         <v>19</v>
       </c>
       <c r="C19">
-        <v>294511.42</v>
+        <v>73624.52</v>
       </c>
       <c r="D19">
-        <v>294511.42</v>
+        <v>73624.52</v>
       </c>
       <c r="E19">
-        <v>294511.42</v>
+        <v>73624.52</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
       </c>
       <c r="C20">
-        <v>73624.52</v>
+        <v>130933.7</v>
       </c>
       <c r="D20">
-        <v>73624.52</v>
+        <v>130933.7</v>
       </c>
       <c r="E20">
-        <v>73624.52</v>
+        <v>130933.7</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B21" t="s">
         <v>21</v>
       </c>
       <c r="C21">
-        <v>130933.7</v>
+        <v>60961.98</v>
       </c>
       <c r="D21">
-        <v>130933.7</v>
+        <v>60961.98</v>
       </c>
       <c r="E21">
-        <v>130933.7</v>
+        <v>60961.98</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B22" t="s">
         <v>22</v>
       </c>
       <c r="C22">
-        <v>60961.98</v>
+        <v>134696.19</v>
       </c>
       <c r="D22">
-        <v>60961.98</v>
+        <v>134696.19</v>
       </c>
       <c r="E22">
-        <v>60961.98</v>
+        <v>134696.19</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
       </c>
       <c r="C23">
-        <v>79821.1</v>
+        <v>804999.6</v>
       </c>
       <c r="D23">
-        <v>79821.1</v>
+        <v>804999.6</v>
       </c>
       <c r="E23">
-        <v>79821.1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>804999.6</v>
+      </c>
+    </row>
+    <row r="24" ht="14.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
       </c>
       <c r="C24">
-        <v>134696.19</v>
+        <v>107772.44</v>
       </c>
       <c r="D24">
-        <v>134696.19</v>
+        <v>107772.44</v>
       </c>
       <c r="E24">
-        <v>134696.19</v>
+        <v>107772.44</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B25" t="s">
         <v>25</v>
       </c>
       <c r="C25">
-        <v>804999.6</v>
+        <v>26359.42</v>
       </c>
       <c r="D25">
-        <v>804999.6</v>
+        <v>26359.42</v>
       </c>
       <c r="E25">
-        <v>804999.6</v>
-      </c>
-    </row>
-    <row r="26" ht="14.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>26359.42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
       </c>
       <c r="C26">
-        <v>107772.44</v>
+        <v>756098.97</v>
       </c>
       <c r="D26">
-        <v>107772.44</v>
+        <v>756098.97</v>
       </c>
       <c r="E26">
-        <v>107772.44</v>
+        <v>756098.97</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="B27" t="s">
         <v>27</v>
       </c>
       <c r="C27">
-        <v>26359.42</v>
+        <v>75979.11</v>
       </c>
       <c r="D27">
-        <v>26359.42</v>
+        <v>75979.11</v>
       </c>
       <c r="E27">
-        <v>26359.42</v>
+        <v>75979.11</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="B28" t="s">
         <v>28</v>
       </c>
       <c r="C28">
-        <v>756098.97</v>
+        <v>13078.73</v>
       </c>
       <c r="D28">
-        <v>756098.97</v>
+        <v>13078.73</v>
       </c>
       <c r="E28">
-        <v>756098.97</v>
+        <v>13078.73</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B29" t="s">
         <v>29</v>
       </c>
       <c r="C29">
-        <v>75979.11</v>
+        <v>1948.5</v>
       </c>
       <c r="D29">
-        <v>75979.11</v>
+        <v>1948.5</v>
       </c>
       <c r="E29">
-        <v>75979.11</v>
+        <v>1948.5</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B30" t="s">
         <v>30</v>
       </c>
       <c r="C30">
-        <v>13078.73</v>
+        <v>10316.84</v>
       </c>
       <c r="D30">
-        <v>13078.73</v>
+        <v>10316.84</v>
       </c>
       <c r="E30">
-        <v>13078.73</v>
+        <v>10316.84</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
       </c>
       <c r="C31">
-        <v>1948.5</v>
+        <v>17436.6</v>
       </c>
       <c r="D31">
-        <v>1948.5</v>
+        <v>17436.6</v>
       </c>
       <c r="E31">
-        <v>1948.5</v>
+        <v>17436.6</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B32" t="s">
         <v>32</v>
       </c>
       <c r="C32">
-        <v>10316.84</v>
+        <v>198710.3</v>
       </c>
       <c r="D32">
-        <v>10316.84</v>
+        <v>198710.3</v>
       </c>
       <c r="E32">
-        <v>10316.84</v>
+        <v>198710.3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="B33" t="s">
         <v>33</v>
       </c>
       <c r="C33">
-        <v>17436.6</v>
+        <v>-33551.21</v>
       </c>
       <c r="D33">
-        <v>17436.6</v>
+        <v>-33551.21</v>
       </c>
       <c r="E33">
-        <v>17436.6</v>
+        <v>-33551.21</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B34" t="s">
         <v>34</v>
       </c>
       <c r="C34">
-        <v>198710.3</v>
+        <v>11635.11</v>
       </c>
       <c r="D34">
-        <v>198710.3</v>
+        <v>11635.11</v>
       </c>
       <c r="E34">
-        <v>198710.3</v>
+        <v>11635.11</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B35" t="s">
         <v>35</v>
       </c>
       <c r="C35">
-        <v>-33551.21</v>
+        <v>105968.02</v>
       </c>
       <c r="D35">
-        <v>-33551.21</v>
+        <v>105968.02</v>
       </c>
       <c r="E35">
-        <v>-33551.21</v>
+        <v>105968.02</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B36" t="s">
         <v>36</v>
       </c>
       <c r="C36">
-        <v>11635.11</v>
+        <v>-549959.08</v>
       </c>
       <c r="D36">
-        <v>11635.11</v>
+        <v>-549959.08</v>
       </c>
       <c r="E36">
-        <v>11635.11</v>
+        <v>-549959.08</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="B37" t="s">
         <v>37</v>
       </c>
       <c r="C37">
-        <v>105968.02</v>
+        <v>216231.6</v>
       </c>
       <c r="D37">
-        <v>105968.02</v>
+        <v>216231.6</v>
       </c>
       <c r="E37">
-        <v>105968.02</v>
+        <v>216231.6</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B38" t="s">
         <v>38</v>
       </c>
       <c r="C38">
-        <v>-549959.08</v>
+        <v>5519.81</v>
       </c>
       <c r="D38">
-        <v>-549959.08</v>
+        <v>5519.81</v>
       </c>
       <c r="E38">
-        <v>-549959.08</v>
+        <v>5519.81</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="B39" t="s">
         <v>39</v>
       </c>
       <c r="C39">
-        <v>216231.6</v>
+        <v>-1880.4</v>
       </c>
       <c r="D39">
-        <v>216231.6</v>
+        <v>-1880.4</v>
       </c>
       <c r="E39">
-        <v>216231.6</v>
+        <v>-1880.4</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="B40" t="s">
         <v>40</v>
       </c>
       <c r="C40">
-        <v>5519.81</v>
+        <v>45136.63</v>
       </c>
       <c r="D40">
-        <v>5519.81</v>
+        <v>45136.63</v>
       </c>
       <c r="E40">
-        <v>5519.81</v>
+        <v>45136.63</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>405</v>
+        <v>444</v>
       </c>
       <c r="B41" t="s">
         <v>41</v>
       </c>
       <c r="C41">
-        <v>-1880.4</v>
+        <v>5678.81</v>
       </c>
       <c r="D41">
-        <v>-1880.4</v>
+        <v>5678.81</v>
       </c>
       <c r="E41">
-        <v>-1880.4</v>
+        <v>5678.81</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>431</v>
+        <v>470</v>
       </c>
       <c r="B42" t="s">
         <v>42</v>
       </c>
       <c r="C42">
-        <v>45136.63</v>
+        <v>738000</v>
       </c>
       <c r="D42">
-        <v>45136.63</v>
+        <v>738000</v>
       </c>
       <c r="E42">
-        <v>45136.63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>444</v>
-      </c>
-      <c r="B43" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43">
-        <v>5678.81</v>
-      </c>
-      <c r="D43">
-        <v>5678.81</v>
-      </c>
-      <c r="E43">
-        <v>5678.81</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>470</v>
-      </c>
-      <c r="B44" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44">
-        <v>738000</v>
-      </c>
-      <c r="D44">
-        <v>738000</v>
-      </c>
-      <c r="E44">
         <v>738000</v>
       </c>
     </row>

--- a/Test Data/Regression/4689052/UK_InHeader_ImportTb02.xlsx
+++ b/Test Data/Regression/4689052/UK_InHeader_ImportTb02.xlsx
@@ -23,13 +23,13 @@
     <t>test Description</t>
   </si>
   <si>
-    <t>2222244_PWE01_1777825842053</t>
-  </si>
-  <si>
-    <t>2222244_PWE02_1777825842053</t>
-  </si>
-  <si>
-    <t>2222244_PWE03_1777825842053</t>
+    <t>2222244_PWE01_1778319778640</t>
+  </si>
+  <si>
+    <t>2222244_PWE02_1778319778640</t>
+  </si>
+  <si>
+    <t>2222244_PWE03_1778319778640</t>
   </si>
   <si>
     <t>Sale of goods, UK</t>

--- a/Test Data/Regression/4689052/UK_InHeader_ImportTb02.xlsx
+++ b/Test Data/Regression/4689052/UK_InHeader_ImportTb02.xlsx
@@ -23,13 +23,13 @@
     <t>test Description</t>
   </si>
   <si>
-    <t>2222244_PWE01_1778319778640</t>
-  </si>
-  <si>
-    <t>2222244_PWE02_1778319778640</t>
-  </si>
-  <si>
-    <t>2222244_PWE03_1778319778640</t>
+    <t>2222244_PWE01_1778649278785</t>
+  </si>
+  <si>
+    <t>2222244_PWE02_1778649278785</t>
+  </si>
+  <si>
+    <t>2222244_PWE03_1778649278785</t>
   </si>
   <si>
     <t>Sale of goods, UK</t>
